--- a/export/asdasda - Seguimiento.xlsx
+++ b/export/asdasda - Seguimiento.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="95">
   <si>
     <t>NOMBRE Y APELLIDO</t>
   </si>
@@ -26,6 +26,21 @@
   </si>
   <si>
     <t>EVALUACIÓN 4</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN 5</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN 6</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN 7</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN 9</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN 8</t>
   </si>
   <si>
     <t xml:space="preserve">PROMEDIO
@@ -738,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:AL82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -750,11 +765,21 @@
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="16" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="18" customWidth="1"/>
+    <col min="24" max="26" width="14" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="28" max="30" width="14" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
+    <col min="32" max="34" width="14" customWidth="1"/>
+    <col min="35" max="35" width="18" customWidth="1"/>
+    <col min="36" max="37" width="14" customWidth="1"/>
+    <col min="38" max="38" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -785,62 +810,152 @@
       <c r="R1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" ht="28" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL2" s="2"/>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" s="6">
         <v>2</v>
@@ -890,13 +1005,51 @@
       <c r="Q3" s="7">
         <v>4</v>
       </c>
-      <c r="R3" s="8">
-        <v>4.5</v>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6">
+        <v>4</v>
+      </c>
+      <c r="T3" s="6"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6">
+        <v>4</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="8">
+        <v>3</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6">
         <v>2</v>
@@ -905,10 +1058,10 @@
         <v>3.8</v>
       </c>
       <c r="D4" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E4" s="7">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F4" s="6">
         <v>7</v>
@@ -929,10 +1082,10 @@
         <v>3.8</v>
       </c>
       <c r="L4" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M4" s="7">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N4" s="6">
         <v>4</v>
@@ -946,13 +1099,51 @@
       <c r="Q4" s="7">
         <v>3.5</v>
       </c>
-      <c r="R4" s="8">
-        <v>3.9</v>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="T4" s="6"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>2.5</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B5" s="6">
         <v>7</v>
@@ -1002,20 +1193,62 @@
       <c r="Q5" s="7">
         <v>5</v>
       </c>
-      <c r="R5" s="8">
-        <v>6</v>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6">
+        <v>4</v>
+      </c>
+      <c r="T5" s="6"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6">
+        <v>4</v>
+      </c>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="7">
+        <v>7</v>
+      </c>
+      <c r="AH5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="8">
+        <v>5.3</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6">
         <v>3.9</v>
       </c>
       <c r="D6" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E6" s="7">
         <v>0</v>
@@ -1035,7 +1268,7 @@
         <v>3.9</v>
       </c>
       <c r="L6" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M6" s="7">
         <v>0</v>
@@ -1050,20 +1283,58 @@
       <c r="Q6" s="7">
         <v>0</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="6"/>
+      <c r="S6" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T6" s="6"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6">
         <v>4</v>
       </c>
       <c r="D7" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E7" s="7">
         <v>0</v>
@@ -1083,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M7" s="7">
         <v>0</v>
@@ -1098,13 +1369,51 @@
       <c r="Q7" s="7">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="6"/>
+      <c r="S7" s="6">
+        <v>4</v>
+      </c>
+      <c r="T7" s="6"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6">
+        <v>4</v>
+      </c>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6">
@@ -1146,20 +1455,58 @@
       <c r="Q8" s="7">
         <v>0</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="6"/>
+      <c r="S8" s="6">
+        <v>4</v>
+      </c>
+      <c r="T8" s="6"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6">
+        <v>4</v>
+      </c>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6">
         <v>3.8</v>
       </c>
       <c r="D9" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E9" s="7">
         <v>0</v>
@@ -1179,7 +1526,7 @@
         <v>3.8</v>
       </c>
       <c r="L9" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M9" s="7">
         <v>0</v>
@@ -1194,20 +1541,58 @@
       <c r="Q9" s="7">
         <v>0</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="6"/>
+      <c r="S9" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="T9" s="6"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="6"/>
+      <c r="AI9" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AJ9" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6">
         <v>4</v>
       </c>
       <c r="D10" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E10" s="7">
         <v>0</v>
@@ -1227,7 +1612,7 @@
         <v>4</v>
       </c>
       <c r="L10" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M10" s="7">
         <v>0</v>
@@ -1242,13 +1627,51 @@
       <c r="Q10" s="7">
         <v>0</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="6"/>
+      <c r="S10" s="6">
+        <v>4</v>
+      </c>
+      <c r="T10" s="6"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6">
+        <v>4</v>
+      </c>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B11" s="6">
         <v>4</v>
@@ -1298,13 +1721,51 @@
       <c r="Q11" s="7">
         <v>5.3</v>
       </c>
-      <c r="R11" s="8">
-        <v>5</v>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T11" s="6"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="8">
+        <v>3.4</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6">
@@ -1346,13 +1807,51 @@
       <c r="Q12" s="7">
         <v>0</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="6"/>
+      <c r="S12" s="6">
+        <v>4</v>
+      </c>
+      <c r="T12" s="6"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6">
+        <v>4</v>
+      </c>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6">
@@ -1394,13 +1893,51 @@
       <c r="Q13" s="7">
         <v>0</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="6"/>
+      <c r="S13" s="6">
+        <v>4</v>
+      </c>
+      <c r="T13" s="6"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6">
+        <v>4</v>
+      </c>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6">
@@ -1442,13 +1979,51 @@
       <c r="Q14" s="7">
         <v>0</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="6"/>
+      <c r="S14" s="6">
+        <v>4</v>
+      </c>
+      <c r="T14" s="6"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6">
+        <v>4</v>
+      </c>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B15" s="6">
         <v>7</v>
@@ -1498,13 +2073,55 @@
       <c r="Q15" s="7">
         <v>5</v>
       </c>
-      <c r="R15" s="8">
-        <v>6</v>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6">
+        <v>4</v>
+      </c>
+      <c r="T15" s="6"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6">
+        <v>4</v>
+      </c>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="7">
+        <v>7</v>
+      </c>
+      <c r="AH15" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="8">
+        <v>5.3</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B16" s="6">
         <v>2</v>
@@ -1554,13 +2171,51 @@
       <c r="Q16" s="7">
         <v>4</v>
       </c>
-      <c r="R16" s="8">
-        <v>4.5</v>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6">
+        <v>4</v>
+      </c>
+      <c r="T16" s="6"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6">
+        <v>4</v>
+      </c>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="8">
+        <v>3</v>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6">
@@ -1602,13 +2257,51 @@
       <c r="Q17" s="7">
         <v>0</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="6"/>
+      <c r="S17" s="6">
+        <v>4</v>
+      </c>
+      <c r="T17" s="6"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6">
+        <v>4</v>
+      </c>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6">
@@ -1650,13 +2343,51 @@
       <c r="Q18" s="7">
         <v>0</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="6"/>
+      <c r="S18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T18" s="6"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6">
         <v>6</v>
@@ -1706,13 +2437,55 @@
       <c r="Q19" s="7">
         <v>7</v>
       </c>
-      <c r="R19" s="8">
-        <v>6.6</v>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="T19" s="6"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="7">
+        <v>6.1</v>
+      </c>
+      <c r="AH19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="AJ19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="8">
+        <v>5.6</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6">
@@ -1754,13 +2527,51 @@
       <c r="Q20" s="7">
         <v>0</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="6"/>
+      <c r="S20" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="T20" s="6"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="AF20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="AJ20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6">
@@ -1802,13 +2613,51 @@
       <c r="Q21" s="7">
         <v>0</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="6"/>
+      <c r="S21" s="6">
+        <v>4</v>
+      </c>
+      <c r="T21" s="6"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6">
+        <v>4</v>
+      </c>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="6"/>
+      <c r="AI21" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ21" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6">
         <v>6</v>
@@ -1817,10 +2666,10 @@
         <v>1</v>
       </c>
       <c r="D22" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E22" s="7">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F22" s="6">
         <v>5</v>
@@ -1839,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M22" s="7">
         <v>0</v>
@@ -1856,13 +2705,51 @@
       <c r="Q22" s="7">
         <v>1.9</v>
       </c>
-      <c r="R22" s="8">
-        <v>1.4</v>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6">
+        <v>1</v>
+      </c>
+      <c r="T22" s="6"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6">
+        <v>1</v>
+      </c>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="7"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG22" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="6"/>
+      <c r="AI22" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK22" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="8">
+        <v>0.9</v>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B23" s="6">
         <v>5</v>
@@ -1908,13 +2795,51 @@
       <c r="Q23" s="7">
         <v>0</v>
       </c>
-      <c r="R23" s="8">
-        <v>2.5</v>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T23" s="6"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="8">
+        <v>1.7</v>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B24" s="6">
         <v>6</v>
@@ -1964,13 +2889,51 @@
       <c r="Q24" s="7">
         <v>2.7</v>
       </c>
-      <c r="R24" s="8">
-        <v>4.8</v>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="T24" s="6"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AF24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AJ24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="8">
+        <v>3.2</v>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -2020,13 +2983,55 @@
       <c r="Q25" s="7">
         <v>6.9</v>
       </c>
-      <c r="R25" s="8">
-        <v>6.4</v>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="T25" s="6"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE25" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="AF25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="AH25" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="AJ25" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL25" s="8">
+        <v>5.4</v>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6">
         <v>6</v>
@@ -2076,20 +3081,62 @@
       <c r="Q26" s="7">
         <v>6.1</v>
       </c>
-      <c r="R26" s="8">
-        <v>5.7</v>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="T26" s="6"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="7"/>
+      <c r="AD26" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="AF26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="7">
+        <v>5.2</v>
+      </c>
+      <c r="AH26" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="AL26" s="8">
+        <v>4.8</v>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6">
         <v>3.7</v>
       </c>
       <c r="D27" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E27" s="7">
         <v>0</v>
@@ -2109,7 +3156,7 @@
         <v>3.7</v>
       </c>
       <c r="L27" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M27" s="7">
         <v>0</v>
@@ -2124,13 +3171,51 @@
       <c r="Q27" s="7">
         <v>0</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="6"/>
+      <c r="S27" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="T27" s="6"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="7"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="7"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG27" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6"/>
+      <c r="AI27" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK27" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B28" s="6">
         <v>6</v>
@@ -2178,13 +3263,51 @@
       <c r="Q28" s="7">
         <v>7</v>
       </c>
-      <c r="R28" s="8">
-        <v>5.3</v>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6">
+        <v>4</v>
+      </c>
+      <c r="T28" s="6"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6">
+        <v>4</v>
+      </c>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="7"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="8">
+        <v>3.5</v>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6">
@@ -2226,13 +3349,51 @@
       <c r="Q29" s="7">
         <v>0</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="6"/>
+      <c r="S29" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="T29" s="6"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="7"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="AF29" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="6"/>
+      <c r="AI29" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="AJ29" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6">
         <v>4</v>
@@ -2282,13 +3443,51 @@
       <c r="Q30" s="7">
         <v>3.8</v>
       </c>
-      <c r="R30" s="8">
-        <v>3.6</v>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="T30" s="6"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="7"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AF30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6"/>
+      <c r="AI30" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AJ30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="8">
+        <v>2.4</v>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6">
@@ -2330,13 +3529,51 @@
       <c r="Q31" s="7">
         <v>0</v>
       </c>
-      <c r="R31" s="8">
+      <c r="R31" s="6"/>
+      <c r="S31" s="6">
+        <v>4</v>
+      </c>
+      <c r="T31" s="6"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6">
+        <v>4</v>
+      </c>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6"/>
+      <c r="AI31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6">
@@ -2378,13 +3615,51 @@
       <c r="Q32" s="7">
         <v>0</v>
       </c>
-      <c r="R32" s="8">
+      <c r="R32" s="6"/>
+      <c r="S32" s="6">
+        <v>4</v>
+      </c>
+      <c r="T32" s="6"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6">
+        <v>4</v>
+      </c>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="7"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="7"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6">
@@ -2426,13 +3701,51 @@
       <c r="Q33" s="7">
         <v>0</v>
       </c>
-      <c r="R33" s="8">
+      <c r="R33" s="6"/>
+      <c r="S33" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="T33" s="6"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="7"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="6"/>
+      <c r="AE33" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="6"/>
+      <c r="AI33" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B34" s="6">
         <v>6</v>
@@ -2480,13 +3793,51 @@
       <c r="Q34" s="7">
         <v>7</v>
       </c>
-      <c r="R34" s="8">
-        <v>5.3</v>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6">
+        <v>4</v>
+      </c>
+      <c r="T34" s="6"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6">
+        <v>4</v>
+      </c>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="7"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="8">
+        <v>3.5</v>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B35" s="6">
         <v>5</v>
@@ -2532,13 +3883,51 @@
       <c r="Q35" s="7">
         <v>0</v>
       </c>
-      <c r="R35" s="8">
-        <v>2.6</v>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6">
+        <v>4</v>
+      </c>
+      <c r="T35" s="6"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="6"/>
+      <c r="W35" s="6">
+        <v>4</v>
+      </c>
+      <c r="X35" s="6"/>
+      <c r="Y35" s="7"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="7"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="8">
+        <v>1.7</v>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6">
@@ -2580,13 +3969,51 @@
       <c r="Q36" s="7">
         <v>0</v>
       </c>
-      <c r="R36" s="8">
+      <c r="R36" s="6"/>
+      <c r="S36" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="T36" s="6"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="7"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="7"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6"/>
+      <c r="AI36" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6">
@@ -2628,13 +4055,51 @@
       <c r="Q37" s="7">
         <v>0</v>
       </c>
-      <c r="R37" s="8">
+      <c r="R37" s="6"/>
+      <c r="S37" s="6">
+        <v>4</v>
+      </c>
+      <c r="T37" s="6"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="6"/>
+      <c r="W37" s="6">
+        <v>4</v>
+      </c>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="7"/>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF37" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="6"/>
+      <c r="AI37" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ37" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6">
@@ -2676,13 +4141,51 @@
       <c r="Q38" s="7">
         <v>0</v>
       </c>
-      <c r="R38" s="8">
+      <c r="R38" s="6"/>
+      <c r="S38" s="6">
+        <v>4</v>
+      </c>
+      <c r="T38" s="6"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="6"/>
+      <c r="W38" s="6">
+        <v>4</v>
+      </c>
+      <c r="X38" s="6"/>
+      <c r="Y38" s="7"/>
+      <c r="Z38" s="6"/>
+      <c r="AA38" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB38" s="6"/>
+      <c r="AC38" s="7"/>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="6"/>
+      <c r="AI38" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6">
@@ -2724,13 +4227,51 @@
       <c r="Q39" s="7">
         <v>0</v>
       </c>
-      <c r="R39" s="8">
+      <c r="R39" s="6"/>
+      <c r="S39" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="T39" s="6"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6"/>
+      <c r="AI39" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6">
@@ -2772,13 +4313,51 @@
       <c r="Q40" s="7">
         <v>0</v>
       </c>
-      <c r="R40" s="8">
+      <c r="R40" s="6"/>
+      <c r="S40" s="6">
+        <v>4</v>
+      </c>
+      <c r="T40" s="6"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6">
+        <v>4</v>
+      </c>
+      <c r="X40" s="6"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB40" s="6"/>
+      <c r="AC40" s="7"/>
+      <c r="AD40" s="6"/>
+      <c r="AE40" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="6"/>
+      <c r="AI40" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ40" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6">
@@ -2820,20 +4399,58 @@
       <c r="Q41" s="7">
         <v>0</v>
       </c>
-      <c r="R41" s="8">
+      <c r="R41" s="6"/>
+      <c r="S41" s="6">
+        <v>4</v>
+      </c>
+      <c r="T41" s="6"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6">
+        <v>4</v>
+      </c>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="7"/>
+      <c r="AD41" s="6"/>
+      <c r="AE41" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="6"/>
+      <c r="AI41" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ41" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6">
         <v>3.9</v>
       </c>
       <c r="D42" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E42" s="7">
         <v>0</v>
@@ -2853,7 +4470,7 @@
         <v>3.9</v>
       </c>
       <c r="L42" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M42" s="7">
         <v>0</v>
@@ -2868,13 +4485,51 @@
       <c r="Q42" s="7">
         <v>0</v>
       </c>
-      <c r="R42" s="8">
+      <c r="R42" s="6"/>
+      <c r="S42" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T42" s="6"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="7"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6"/>
+      <c r="AI42" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK42" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6">
@@ -2916,20 +4571,58 @@
       <c r="Q43" s="7">
         <v>0</v>
       </c>
-      <c r="R43" s="8">
+      <c r="R43" s="6"/>
+      <c r="S43" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T43" s="6"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X43" s="6"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="7"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6"/>
+      <c r="AI43" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6">
         <v>3.6</v>
       </c>
       <c r="D44" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E44" s="7">
         <v>0</v>
@@ -2949,7 +4642,7 @@
         <v>3.6</v>
       </c>
       <c r="L44" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M44" s="7">
         <v>0</v>
@@ -2964,13 +4657,51 @@
       <c r="Q44" s="7">
         <v>0</v>
       </c>
-      <c r="R44" s="8">
+      <c r="R44" s="6"/>
+      <c r="S44" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="T44" s="6"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="6"/>
+      <c r="W44" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="X44" s="6"/>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="7"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="AF44" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG44" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="6"/>
+      <c r="AI44" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="AJ44" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK44" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B45" s="6">
         <v>3</v>
@@ -3020,20 +4751,58 @@
       <c r="Q45" s="7">
         <v>5.5</v>
       </c>
-      <c r="R45" s="8">
-        <v>5.5</v>
+      <c r="R45" s="6"/>
+      <c r="S45" s="6">
+        <v>4</v>
+      </c>
+      <c r="T45" s="6"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="6"/>
+      <c r="W45" s="6">
+        <v>4</v>
+      </c>
+      <c r="X45" s="6"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="7"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="6"/>
+      <c r="AI45" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ45" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="8">
+        <v>3.7</v>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6">
         <v>3.9</v>
       </c>
       <c r="D46" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E46" s="7">
         <v>0</v>
@@ -3053,7 +4822,7 @@
         <v>3.9</v>
       </c>
       <c r="L46" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M46" s="7">
         <v>0</v>
@@ -3068,20 +4837,58 @@
       <c r="Q46" s="7">
         <v>0</v>
       </c>
-      <c r="R46" s="8">
+      <c r="R46" s="6"/>
+      <c r="S46" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T46" s="6"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="6"/>
+      <c r="W46" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X46" s="6"/>
+      <c r="Y46" s="7"/>
+      <c r="Z46" s="6"/>
+      <c r="AA46" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="7"/>
+      <c r="AD46" s="6"/>
+      <c r="AE46" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6"/>
+      <c r="AI46" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK46" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6">
         <v>3.2</v>
       </c>
       <c r="D47" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E47" s="7">
         <v>0</v>
@@ -3101,7 +4908,7 @@
         <v>3.2</v>
       </c>
       <c r="L47" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M47" s="7">
         <v>0</v>
@@ -3116,13 +4923,51 @@
       <c r="Q47" s="7">
         <v>0</v>
       </c>
-      <c r="R47" s="8">
+      <c r="R47" s="6"/>
+      <c r="S47" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="T47" s="6"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="6"/>
+      <c r="W47" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="X47" s="6"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="7"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AF47" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="6"/>
+      <c r="AI47" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="AJ47" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK47" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B48" s="6">
         <v>3</v>
@@ -3172,13 +5017,51 @@
       <c r="Q48" s="7">
         <v>5.5</v>
       </c>
-      <c r="R48" s="8">
-        <v>5.5</v>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6">
+        <v>4</v>
+      </c>
+      <c r="T48" s="6"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="6"/>
+      <c r="W48" s="6">
+        <v>4</v>
+      </c>
+      <c r="X48" s="6"/>
+      <c r="Y48" s="7"/>
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="7"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="6"/>
+      <c r="AI48" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ48" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="8">
+        <v>3.7</v>
       </c>
     </row>
-    <row r="49" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6">
@@ -3220,13 +5103,51 @@
       <c r="Q49" s="7">
         <v>0</v>
       </c>
-      <c r="R49" s="8">
+      <c r="R49" s="6"/>
+      <c r="S49" s="6">
+        <v>4</v>
+      </c>
+      <c r="T49" s="6"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="6"/>
+      <c r="W49" s="6">
+        <v>4</v>
+      </c>
+      <c r="X49" s="6"/>
+      <c r="Y49" s="7"/>
+      <c r="Z49" s="6"/>
+      <c r="AA49" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB49" s="6"/>
+      <c r="AC49" s="7"/>
+      <c r="AD49" s="6"/>
+      <c r="AE49" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="6"/>
+      <c r="AI49" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6">
@@ -3268,13 +5189,51 @@
       <c r="Q50" s="7">
         <v>0</v>
       </c>
-      <c r="R50" s="8">
+      <c r="R50" s="6"/>
+      <c r="S50" s="6">
+        <v>4</v>
+      </c>
+      <c r="T50" s="6"/>
+      <c r="U50" s="7"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6">
+        <v>4</v>
+      </c>
+      <c r="X50" s="6"/>
+      <c r="Y50" s="7"/>
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="7"/>
+      <c r="AD50" s="6"/>
+      <c r="AE50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6"/>
+      <c r="AI50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6">
@@ -3316,13 +5275,51 @@
       <c r="Q51" s="7">
         <v>0</v>
       </c>
-      <c r="R51" s="8">
+      <c r="R51" s="6"/>
+      <c r="S51" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T51" s="6"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X51" s="6"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="7"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6"/>
+      <c r="AI51" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B52" s="6">
         <v>6</v>
@@ -3331,10 +5328,10 @@
         <v>2.4</v>
       </c>
       <c r="D52" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E52" s="7">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="F52" s="6">
         <v>5</v>
@@ -3353,7 +5350,7 @@
         <v>2.4</v>
       </c>
       <c r="L52" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M52" s="7">
         <v>0</v>
@@ -3370,13 +5367,51 @@
       <c r="Q52" s="7">
         <v>4.6</v>
       </c>
-      <c r="R52" s="8">
-        <v>3.2</v>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="T52" s="6"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="X52" s="6"/>
+      <c r="Y52" s="7"/>
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="7"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="6"/>
+      <c r="AI52" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK52" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="8">
+        <v>2.1</v>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B53" s="6">
         <v>6</v>
@@ -3426,13 +5461,51 @@
       <c r="Q53" s="7">
         <v>3.4</v>
       </c>
-      <c r="R53" s="8">
-        <v>6</v>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6">
+        <v>4</v>
+      </c>
+      <c r="T53" s="6"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="6"/>
+      <c r="W53" s="6">
+        <v>4</v>
+      </c>
+      <c r="X53" s="6"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="6"/>
+      <c r="AA53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB53" s="6"/>
+      <c r="AC53" s="7"/>
+      <c r="AD53" s="6"/>
+      <c r="AE53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6"/>
+      <c r="AI53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="8">
+        <v>4</v>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6">
@@ -3474,13 +5547,51 @@
       <c r="Q54" s="7">
         <v>0</v>
       </c>
-      <c r="R54" s="8">
+      <c r="R54" s="6"/>
+      <c r="S54" s="6">
+        <v>4</v>
+      </c>
+      <c r="T54" s="6"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="6"/>
+      <c r="W54" s="6">
+        <v>4</v>
+      </c>
+      <c r="X54" s="6"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="6"/>
+      <c r="AA54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB54" s="6"/>
+      <c r="AC54" s="7"/>
+      <c r="AD54" s="6"/>
+      <c r="AE54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="6"/>
+      <c r="AI54" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ54" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="6">
@@ -3522,13 +5633,51 @@
       <c r="Q55" s="7">
         <v>0</v>
       </c>
-      <c r="R55" s="8">
+      <c r="R55" s="6"/>
+      <c r="S55" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="T55" s="6"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="6"/>
+      <c r="W55" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="X55" s="6"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="6"/>
+      <c r="AA55" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AB55" s="6"/>
+      <c r="AC55" s="7"/>
+      <c r="AD55" s="6"/>
+      <c r="AE55" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6"/>
+      <c r="AI55" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B56" s="6">
         <v>3</v>
@@ -3578,13 +5727,51 @@
       <c r="Q56" s="7">
         <v>5.5</v>
       </c>
-      <c r="R56" s="8">
-        <v>5.5</v>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6">
+        <v>4</v>
+      </c>
+      <c r="T56" s="6"/>
+      <c r="U56" s="7"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="6">
+        <v>4</v>
+      </c>
+      <c r="X56" s="6"/>
+      <c r="Y56" s="7"/>
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB56" s="6"/>
+      <c r="AC56" s="7"/>
+      <c r="AD56" s="6"/>
+      <c r="AE56" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH56" s="6"/>
+      <c r="AI56" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ56" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL56" s="8">
+        <v>3.7</v>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B57" s="6">
         <v>5</v>
@@ -3630,13 +5817,51 @@
       <c r="Q57" s="7">
         <v>0</v>
       </c>
-      <c r="R57" s="8">
-        <v>2.6</v>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6">
+        <v>4</v>
+      </c>
+      <c r="T57" s="6"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="6"/>
+      <c r="W57" s="6">
+        <v>4</v>
+      </c>
+      <c r="X57" s="6"/>
+      <c r="Y57" s="7"/>
+      <c r="Z57" s="6"/>
+      <c r="AA57" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB57" s="6"/>
+      <c r="AC57" s="7"/>
+      <c r="AD57" s="6"/>
+      <c r="AE57" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="6"/>
+      <c r="AI57" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ57" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="8">
+        <v>1.7</v>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B58" s="6">
         <v>5</v>
@@ -3645,10 +5870,10 @@
         <v>3.7</v>
       </c>
       <c r="D58" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E58" s="7">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="6">
         <v>5</v>
@@ -3667,7 +5892,7 @@
         <v>3.7</v>
       </c>
       <c r="L58" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M58" s="7">
         <v>0</v>
@@ -3682,13 +5907,51 @@
       <c r="Q58" s="7">
         <v>0</v>
       </c>
-      <c r="R58" s="8">
-        <v>2.2</v>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="T58" s="6"/>
+      <c r="U58" s="7"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="X58" s="6"/>
+      <c r="Y58" s="7"/>
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AB58" s="6"/>
+      <c r="AC58" s="7"/>
+      <c r="AD58" s="6"/>
+      <c r="AE58" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG58" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6"/>
+      <c r="AI58" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK58" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="8">
+        <v>1.4</v>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6">
@@ -3730,13 +5993,51 @@
       <c r="Q59" s="7">
         <v>0</v>
       </c>
-      <c r="R59" s="8">
+      <c r="R59" s="6"/>
+      <c r="S59" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="T59" s="6"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="6"/>
+      <c r="W59" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="X59" s="6"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="AB59" s="6"/>
+      <c r="AC59" s="7"/>
+      <c r="AD59" s="6"/>
+      <c r="AE59" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="AF59" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="6"/>
+      <c r="AI59" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="AJ59" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6">
@@ -3778,13 +6079,51 @@
       <c r="Q60" s="7">
         <v>0</v>
       </c>
-      <c r="R60" s="8">
+      <c r="R60" s="6"/>
+      <c r="S60" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="T60" s="6"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="6"/>
+      <c r="W60" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="X60" s="6"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="6"/>
+      <c r="AA60" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AB60" s="6"/>
+      <c r="AC60" s="7"/>
+      <c r="AD60" s="6"/>
+      <c r="AE60" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AF60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="6"/>
+      <c r="AI60" s="6">
+        <v>3.7</v>
+      </c>
+      <c r="AJ60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6">
@@ -3826,13 +6165,51 @@
       <c r="Q61" s="7">
         <v>0</v>
       </c>
-      <c r="R61" s="8">
+      <c r="R61" s="6"/>
+      <c r="S61" s="6">
+        <v>4</v>
+      </c>
+      <c r="T61" s="6"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="6"/>
+      <c r="W61" s="6">
+        <v>4</v>
+      </c>
+      <c r="X61" s="6"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="6"/>
+      <c r="AA61" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB61" s="6"/>
+      <c r="AC61" s="7"/>
+      <c r="AD61" s="6"/>
+      <c r="AE61" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="6"/>
+      <c r="AI61" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6">
@@ -3874,13 +6251,51 @@
       <c r="Q62" s="7">
         <v>0</v>
       </c>
-      <c r="R62" s="8">
+      <c r="R62" s="6"/>
+      <c r="S62" s="6">
+        <v>4</v>
+      </c>
+      <c r="T62" s="6"/>
+      <c r="U62" s="7"/>
+      <c r="V62" s="6"/>
+      <c r="W62" s="6">
+        <v>4</v>
+      </c>
+      <c r="X62" s="6"/>
+      <c r="Y62" s="7"/>
+      <c r="Z62" s="6"/>
+      <c r="AA62" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="6"/>
+      <c r="AC62" s="7"/>
+      <c r="AD62" s="6"/>
+      <c r="AE62" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6"/>
+      <c r="AI62" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B63" s="6">
         <v>7</v>
@@ -3889,10 +6304,10 @@
         <v>4</v>
       </c>
       <c r="D63" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E63" s="7">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="F63" s="6">
         <v>6</v>
@@ -3913,10 +6328,10 @@
         <v>4</v>
       </c>
       <c r="L63" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M63" s="7">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="N63" s="6">
         <v>5</v>
@@ -3930,20 +6345,62 @@
       <c r="Q63" s="7">
         <v>4.5</v>
       </c>
-      <c r="R63" s="8">
-        <v>5.4</v>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6">
+        <v>4</v>
+      </c>
+      <c r="T63" s="6"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6">
+        <v>4</v>
+      </c>
+      <c r="X63" s="6"/>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="6"/>
+      <c r="AA63" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB63" s="6"/>
+      <c r="AC63" s="7"/>
+      <c r="AD63" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE63" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF63" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG63" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="AH63" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI63" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ63" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK63" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="AL63" s="8">
+        <v>4.7</v>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6">
         <v>4</v>
       </c>
       <c r="D64" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E64" s="7">
         <v>0</v>
@@ -3963,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="L64" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M64" s="7">
         <v>0</v>
@@ -3978,13 +6435,51 @@
       <c r="Q64" s="7">
         <v>0</v>
       </c>
-      <c r="R64" s="8">
+      <c r="R64" s="6"/>
+      <c r="S64" s="6">
+        <v>4</v>
+      </c>
+      <c r="T64" s="6"/>
+      <c r="U64" s="7"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="6">
+        <v>4</v>
+      </c>
+      <c r="X64" s="6"/>
+      <c r="Y64" s="7"/>
+      <c r="Z64" s="6"/>
+      <c r="AA64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB64" s="6"/>
+      <c r="AC64" s="7"/>
+      <c r="AD64" s="6"/>
+      <c r="AE64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF64" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG64" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="6"/>
+      <c r="AI64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ64" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK64" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL64" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B65" s="6">
         <v>2</v>
@@ -4034,13 +6529,51 @@
       <c r="Q65" s="7">
         <v>4</v>
       </c>
-      <c r="R65" s="8">
-        <v>4.5</v>
+      <c r="R65" s="6"/>
+      <c r="S65" s="6">
+        <v>4</v>
+      </c>
+      <c r="T65" s="6"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="6"/>
+      <c r="W65" s="6">
+        <v>4</v>
+      </c>
+      <c r="X65" s="6"/>
+      <c r="Y65" s="7"/>
+      <c r="Z65" s="6"/>
+      <c r="AA65" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB65" s="6"/>
+      <c r="AC65" s="7"/>
+      <c r="AD65" s="6"/>
+      <c r="AE65" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF65" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="6"/>
+      <c r="AI65" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ65" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL65" s="8">
+        <v>3</v>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6">
@@ -4082,20 +6615,58 @@
       <c r="Q66" s="7">
         <v>0</v>
       </c>
-      <c r="R66" s="8">
+      <c r="R66" s="6"/>
+      <c r="S66" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="T66" s="6"/>
+      <c r="U66" s="7"/>
+      <c r="V66" s="6"/>
+      <c r="W66" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="X66" s="6"/>
+      <c r="Y66" s="7"/>
+      <c r="Z66" s="6"/>
+      <c r="AA66" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AB66" s="6"/>
+      <c r="AC66" s="7"/>
+      <c r="AD66" s="6"/>
+      <c r="AE66" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AF66" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="6"/>
+      <c r="AI66" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AJ66" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL66" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="67" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6">
         <v>4</v>
       </c>
       <c r="D67" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E67" s="7">
         <v>0</v>
@@ -4115,7 +6686,7 @@
         <v>4</v>
       </c>
       <c r="L67" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M67" s="7">
         <v>0</v>
@@ -4130,13 +6701,51 @@
       <c r="Q67" s="7">
         <v>0</v>
       </c>
-      <c r="R67" s="8">
+      <c r="R67" s="6"/>
+      <c r="S67" s="6">
+        <v>4</v>
+      </c>
+      <c r="T67" s="6"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6">
+        <v>4</v>
+      </c>
+      <c r="X67" s="6"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="6"/>
+      <c r="AA67" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB67" s="6"/>
+      <c r="AC67" s="7"/>
+      <c r="AD67" s="6"/>
+      <c r="AE67" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF67" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG67" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH67" s="6"/>
+      <c r="AI67" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ67" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK67" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL67" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6">
@@ -4178,13 +6787,51 @@
       <c r="Q68" s="7">
         <v>0</v>
       </c>
-      <c r="R68" s="8">
+      <c r="R68" s="6"/>
+      <c r="S68" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="T68" s="6"/>
+      <c r="U68" s="7"/>
+      <c r="V68" s="6"/>
+      <c r="W68" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="X68" s="6"/>
+      <c r="Y68" s="7"/>
+      <c r="Z68" s="6"/>
+      <c r="AA68" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AB68" s="6"/>
+      <c r="AC68" s="7"/>
+      <c r="AD68" s="6"/>
+      <c r="AE68" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AF68" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="6"/>
+      <c r="AI68" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AJ68" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL68" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B69" s="6">
         <v>3</v>
@@ -4193,10 +6840,10 @@
         <v>3.4</v>
       </c>
       <c r="D69" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E69" s="7">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F69" s="6">
         <v>6</v>
@@ -4217,10 +6864,10 @@
         <v>3.4</v>
       </c>
       <c r="L69" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M69" s="7">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N69" s="6">
         <v>5</v>
@@ -4234,13 +6881,51 @@
       <c r="Q69" s="7">
         <v>4.2</v>
       </c>
-      <c r="R69" s="8">
-        <v>4.2</v>
+      <c r="R69" s="6"/>
+      <c r="S69" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="T69" s="6"/>
+      <c r="U69" s="7"/>
+      <c r="V69" s="6"/>
+      <c r="W69" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="X69" s="6"/>
+      <c r="Y69" s="7"/>
+      <c r="Z69" s="6"/>
+      <c r="AA69" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AB69" s="6"/>
+      <c r="AC69" s="7"/>
+      <c r="AD69" s="6"/>
+      <c r="AE69" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AF69" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG69" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="6"/>
+      <c r="AI69" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AJ69" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK69" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL69" s="8">
+        <v>2.7</v>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B70" s="6">
         <v>7</v>
@@ -4249,10 +6934,10 @@
         <v>4</v>
       </c>
       <c r="D70" s="6">
-        <v>0.067</v>
+        <v>0.107</v>
       </c>
       <c r="E70" s="7">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="F70" s="6">
         <v>6</v>
@@ -4273,10 +6958,10 @@
         <v>4</v>
       </c>
       <c r="L70" s="6">
-        <v>0.067</v>
+        <v>0.107</v>
       </c>
       <c r="M70" s="7">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="N70" s="6">
         <v>5</v>
@@ -4290,13 +6975,55 @@
       <c r="Q70" s="7">
         <v>4.7</v>
       </c>
-      <c r="R70" s="8">
-        <v>5.6</v>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6">
+        <v>4</v>
+      </c>
+      <c r="T70" s="6"/>
+      <c r="U70" s="7"/>
+      <c r="V70" s="6"/>
+      <c r="W70" s="6">
+        <v>4</v>
+      </c>
+      <c r="X70" s="6"/>
+      <c r="Y70" s="7"/>
+      <c r="Z70" s="6"/>
+      <c r="AA70" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB70" s="6"/>
+      <c r="AC70" s="7"/>
+      <c r="AD70" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF70" s="6">
+        <v>0.067</v>
+      </c>
+      <c r="AG70" s="7">
+        <v>6.5</v>
+      </c>
+      <c r="AH70" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI70" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ70" s="6">
+        <v>0.067</v>
+      </c>
+      <c r="AK70" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="AL70" s="8">
+        <v>4.9</v>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6">
@@ -4338,13 +7065,51 @@
       <c r="Q71" s="7">
         <v>0</v>
       </c>
-      <c r="R71" s="8">
+      <c r="R71" s="6"/>
+      <c r="S71" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="T71" s="6"/>
+      <c r="U71" s="7"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="X71" s="6"/>
+      <c r="Y71" s="7"/>
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AB71" s="6"/>
+      <c r="AC71" s="7"/>
+      <c r="AD71" s="6"/>
+      <c r="AE71" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6"/>
+      <c r="AI71" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6">
@@ -4386,13 +7151,51 @@
       <c r="Q72" s="7">
         <v>0</v>
       </c>
-      <c r="R72" s="8">
+      <c r="R72" s="6"/>
+      <c r="S72" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="T72" s="6"/>
+      <c r="U72" s="7"/>
+      <c r="V72" s="6"/>
+      <c r="W72" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="X72" s="6"/>
+      <c r="Y72" s="7"/>
+      <c r="Z72" s="6"/>
+      <c r="AA72" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AB72" s="6"/>
+      <c r="AC72" s="7"/>
+      <c r="AD72" s="6"/>
+      <c r="AE72" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AF72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG72" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH72" s="6"/>
+      <c r="AI72" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AJ72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL72" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B73" s="6">
         <v>6</v>
@@ -4442,20 +7245,58 @@
       <c r="Q73" s="7">
         <v>2.8</v>
       </c>
-      <c r="R73" s="8">
-        <v>5</v>
+      <c r="R73" s="6"/>
+      <c r="S73" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="T73" s="6"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="6"/>
+      <c r="W73" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="X73" s="6"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="6"/>
+      <c r="AA73" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="AB73" s="6"/>
+      <c r="AC73" s="7"/>
+      <c r="AD73" s="6"/>
+      <c r="AE73" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="AF73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="6"/>
+      <c r="AI73" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="AJ73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL73" s="8">
+        <v>3.3</v>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6">
         <v>3.8</v>
       </c>
       <c r="D74" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E74" s="7">
         <v>0</v>
@@ -4475,7 +7316,7 @@
         <v>3.8</v>
       </c>
       <c r="L74" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M74" s="7">
         <v>0</v>
@@ -4490,13 +7331,51 @@
       <c r="Q74" s="7">
         <v>0</v>
       </c>
-      <c r="R74" s="8">
+      <c r="R74" s="6"/>
+      <c r="S74" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="T74" s="6"/>
+      <c r="U74" s="7"/>
+      <c r="V74" s="6"/>
+      <c r="W74" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="X74" s="6"/>
+      <c r="Y74" s="7"/>
+      <c r="Z74" s="6"/>
+      <c r="AA74" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AB74" s="6"/>
+      <c r="AC74" s="7"/>
+      <c r="AD74" s="6"/>
+      <c r="AE74" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AF74" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG74" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="6"/>
+      <c r="AI74" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AJ74" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK74" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL74" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B75" s="6">
         <v>3</v>
@@ -4546,13 +7425,51 @@
       <c r="Q75" s="7">
         <v>4</v>
       </c>
-      <c r="R75" s="8">
-        <v>4</v>
+      <c r="R75" s="6"/>
+      <c r="S75" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="T75" s="6"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="6"/>
+      <c r="W75" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="X75" s="6"/>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="6"/>
+      <c r="AA75" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AB75" s="6"/>
+      <c r="AC75" s="7"/>
+      <c r="AD75" s="6"/>
+      <c r="AE75" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6"/>
+      <c r="AI75" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="8">
+        <v>2.6</v>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B76" s="6">
         <v>5</v>
@@ -4598,13 +7515,51 @@
       <c r="Q76" s="7">
         <v>0</v>
       </c>
-      <c r="R76" s="8">
-        <v>2.6</v>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6">
+        <v>4</v>
+      </c>
+      <c r="T76" s="6"/>
+      <c r="U76" s="7"/>
+      <c r="V76" s="6"/>
+      <c r="W76" s="6">
+        <v>4</v>
+      </c>
+      <c r="X76" s="6"/>
+      <c r="Y76" s="7"/>
+      <c r="Z76" s="6"/>
+      <c r="AA76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB76" s="6"/>
+      <c r="AC76" s="7"/>
+      <c r="AD76" s="6"/>
+      <c r="AE76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6"/>
+      <c r="AI76" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL76" s="8">
+        <v>1.7</v>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="6">
@@ -4646,13 +7601,51 @@
       <c r="Q77" s="7">
         <v>0</v>
       </c>
-      <c r="R77" s="8">
+      <c r="R77" s="6"/>
+      <c r="S77" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="T77" s="6"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="6"/>
+      <c r="W77" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="X77" s="6"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="6"/>
+      <c r="AA77" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AB77" s="6"/>
+      <c r="AC77" s="7"/>
+      <c r="AD77" s="6"/>
+      <c r="AE77" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AF77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="6"/>
+      <c r="AI77" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="AJ77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL77" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B78" s="6">
         <v>4</v>
@@ -4702,13 +7695,51 @@
       <c r="Q78" s="7">
         <v>5.4</v>
       </c>
-      <c r="R78" s="8">
-        <v>5.2</v>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6">
+        <v>4</v>
+      </c>
+      <c r="T78" s="6"/>
+      <c r="U78" s="7"/>
+      <c r="V78" s="6"/>
+      <c r="W78" s="6">
+        <v>4</v>
+      </c>
+      <c r="X78" s="6"/>
+      <c r="Y78" s="7"/>
+      <c r="Z78" s="6"/>
+      <c r="AA78" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB78" s="6"/>
+      <c r="AC78" s="7"/>
+      <c r="AD78" s="6"/>
+      <c r="AE78" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="6"/>
+      <c r="AI78" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="8">
+        <v>3.4</v>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B79" s="6">
         <v>6</v>
@@ -4717,10 +7748,10 @@
         <v>4</v>
       </c>
       <c r="D79" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E79" s="7">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="F79" s="6">
         <v>7</v>
@@ -4741,10 +7772,10 @@
         <v>4</v>
       </c>
       <c r="L79" s="6">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="M79" s="7">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="N79" s="6">
         <v>7</v>
@@ -4758,13 +7789,55 @@
       <c r="Q79" s="7">
         <v>7</v>
       </c>
-      <c r="R79" s="8">
-        <v>6.6</v>
+      <c r="R79" s="6"/>
+      <c r="S79" s="6">
+        <v>4</v>
+      </c>
+      <c r="T79" s="6"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="6"/>
+      <c r="W79" s="6">
+        <v>4</v>
+      </c>
+      <c r="X79" s="6"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="6"/>
+      <c r="AA79" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB79" s="6"/>
+      <c r="AC79" s="7"/>
+      <c r="AD79" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE79" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF79" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AG79" s="7">
+        <v>6.1</v>
+      </c>
+      <c r="AH79" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI79" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ79" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="AK79" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL79" s="8">
+        <v>5.4</v>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B80" s="6">
         <v>6</v>
@@ -4814,13 +7887,51 @@
       <c r="Q80" s="7">
         <v>3</v>
       </c>
-      <c r="R80" s="8">
-        <v>5.3</v>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="T80" s="6"/>
+      <c r="U80" s="7"/>
+      <c r="V80" s="6"/>
+      <c r="W80" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="X80" s="6"/>
+      <c r="Y80" s="7"/>
+      <c r="Z80" s="6"/>
+      <c r="AA80" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="AB80" s="6"/>
+      <c r="AC80" s="7"/>
+      <c r="AD80" s="6"/>
+      <c r="AE80" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="AF80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="6"/>
+      <c r="AI80" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="AJ80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="8">
+        <v>3.5</v>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="6">
@@ -4862,13 +7973,51 @@
       <c r="Q81" s="7">
         <v>0</v>
       </c>
-      <c r="R81" s="8">
+      <c r="R81" s="6"/>
+      <c r="S81" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="T81" s="6"/>
+      <c r="U81" s="7"/>
+      <c r="V81" s="6"/>
+      <c r="W81" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="X81" s="6"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="6"/>
+      <c r="AA81" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="AB81" s="6"/>
+      <c r="AC81" s="7"/>
+      <c r="AD81" s="6"/>
+      <c r="AE81" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="AF81" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="6"/>
+      <c r="AI81" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="AJ81" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B82" s="6">
         <v>4</v>
@@ -4918,18 +8067,61 @@
       <c r="Q82" s="7">
         <v>5.4</v>
       </c>
-      <c r="R82" s="8">
-        <v>5.2</v>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6">
+        <v>4</v>
+      </c>
+      <c r="T82" s="6"/>
+      <c r="U82" s="7"/>
+      <c r="V82" s="6"/>
+      <c r="W82" s="6">
+        <v>4</v>
+      </c>
+      <c r="X82" s="6"/>
+      <c r="Y82" s="7"/>
+      <c r="Z82" s="6"/>
+      <c r="AA82" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB82" s="6"/>
+      <c r="AC82" s="7"/>
+      <c r="AD82" s="6"/>
+      <c r="AE82" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF82" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="7">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="6"/>
+      <c r="AI82" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ82" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK82" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="8">
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:M1"/>
     <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="AL1:AL2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
